--- a/public/templates/bojogae-customer-import.xlsx
+++ b/public/templates/bojogae-customer-import.xlsx
@@ -323,7 +323,7 @@
         <x:v>접수일</x:v>
       </x:c>
       <x:c r="B1" s="8" t="str">
-        <x:v>고객 별칭</x:v>
+        <x:v>카톡대화명</x:v>
       </x:c>
       <x:c r="C1" s="8" t="str">
         <x:v>고객명</x:v>
